--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios115.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios115.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.66713972039056</v>
+        <v>31.8366112623612</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.58202581682753</v>
+        <v>30.55075860567021</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.2274515735434</v>
+        <v>22.475614338363</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.38105594845824</v>
+        <v>26.80962418585676</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33.62464578195479</v>
+        <v>31.24562284368986</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.56629325191457</v>
+        <v>30.20884826389776</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.16042334301828</v>
+        <v>31.966862650352</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.68098775813606</v>
+        <v>30.91474151156233</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.89039854913815</v>
+        <v>22.8092408656634</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.60320353781714</v>
+        <v>26.959157228664</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32.91010540782553</v>
+        <v>31.10580049031446</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.95237583678544</v>
+        <v>30.26303204209067</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.1400111524048</v>
+        <v>31.97843790164912</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.98093713419857</v>
+        <v>31.08648395999778</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.62681847609769</v>
+        <v>22.1316608362798</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.11096464770116</v>
+        <v>27.35722206091097</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33.16663886388341</v>
+        <v>31.02076947999769</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.83935825425385</v>
+        <v>29.71550797327097</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.67353501542477</v>
+        <v>32.01925279462051</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.48929796175758</v>
+        <v>29.99923750180195</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.92345575520881</v>
+        <v>22.67712671600163</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.05092785305341</v>
+        <v>27.23110500609275</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32.89111141774449</v>
+        <v>31.45184567520851</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.98595809028695</v>
+        <v>29.65015749557324</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.51606946462087</v>
+        <v>31.73126233136204</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.06984414768824</v>
+        <v>30.45400862326081</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25.54469144650155</v>
+        <v>22.93509557161339</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24.40118292501526</v>
+        <v>27.22340934879423</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>33.60294551510105</v>
+        <v>30.82959752759295</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.01846403337327</v>
+        <v>29.95760343457476</v>
       </c>
     </row>
   </sheetData>
